--- a/reports/excel/selenium-report.xlsx
+++ b/reports/excel/selenium-report.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="347">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -52,7 +52,7 @@
     <t>Additional Remarks</t>
   </si>
   <si>
-    <t>TC_0567</t>
+    <t>TC_9047</t>
   </si>
   <si>
     <t>Functional Testing</t>
@@ -73,7 +73,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.567Z</t>
+    <t>2026-06-18T06:05:09.047Z</t>
   </si>
   <si>
     <t>N/A</t>
@@ -82,484 +82,445 @@
     <t/>
   </si>
   <si>
-    <t>TC_0569</t>
+    <t>TC_9048</t>
   </si>
   <si>
     <t>TC_AUTH_002: should validate invalid login</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.569Z</t>
-  </si>
-  <si>
-    <t>TC_0570</t>
+    <t>2026-06-18T06:05:09.048Z</t>
+  </si>
+  <si>
+    <t>TC_9049</t>
   </si>
   <si>
     <t>TC_AUTH_003: should validate empty credentials</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.570Z</t>
-  </si>
-  <si>
-    <t>TC_0571</t>
+    <t>2026-06-18T06:05:09.049Z</t>
+  </si>
+  <si>
+    <t>TC_9050</t>
   </si>
   <si>
     <t>TC_AUTH_004: should validate forgot password flow</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.571Z</t>
-  </si>
-  <si>
-    <t>TC_0574</t>
+    <t>2026-06-18T06:05:09.050Z</t>
+  </si>
+  <si>
+    <t>TC_9052</t>
   </si>
   <si>
     <t>TC_AUTH_005: should validate user registration</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.574Z</t>
+    <t>2026-06-18T06:05:09.052Z</t>
+  </si>
+  <si>
+    <t>TC_9053</t>
   </si>
   <si>
     <t>TC_AUTH_006: should handle duplicate account registration</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.575Z</t>
-  </si>
-  <si>
-    <t>TC_0576</t>
+    <t>2026-06-18T06:05:09.053Z</t>
+  </si>
+  <si>
+    <t>TC_9054</t>
   </si>
   <si>
     <t>TC_AUTH_007: should validate logout functionality</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.576Z</t>
-  </si>
-  <si>
-    <t>TC_0577</t>
+    <t>2026-06-18T06:05:09.054Z</t>
   </si>
   <si>
     <t>TC_AUTH_008: should handle session timeout</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.577Z</t>
-  </si>
-  <si>
-    <t>TC_0579</t>
+    <t>TC_9055</t>
   </si>
   <si>
     <t>TC_AUTH_009: should validate login with unverified email</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.579Z</t>
+    <t>2026-06-18T06:05:09.055Z</t>
+  </si>
+  <si>
+    <t>TC_9056</t>
   </si>
   <si>
     <t>TC_AUTH_010: should validate login with suspended account</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.580Z</t>
-  </si>
-  <si>
-    <t>TC_0580</t>
+    <t>2026-06-18T06:05:09.056Z</t>
+  </si>
+  <si>
+    <t>TC_9057</t>
   </si>
   <si>
     <t>TC_AUTH_011: should validate password reset token expiration</t>
   </si>
   <si>
-    <t>TC_0581</t>
+    <t>2026-06-18T06:05:09.057Z</t>
   </si>
   <si>
     <t>TC_AUTH_012: should validate remember me functionality</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.581Z</t>
-  </si>
-  <si>
-    <t>TC_0583</t>
+    <t>TC_9059</t>
   </si>
   <si>
     <t>TC_CRUD_001: Create new record with valid data</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.583Z</t>
+    <t>2026-06-18T06:05:09.059Z</t>
   </si>
   <si>
     <t>TC_CRUD_002: Create new record with missing required fields</t>
   </si>
   <si>
-    <t>TC_0584</t>
+    <t>TC_9060</t>
   </si>
   <si>
     <t>TC_CRUD_003: Read existing record details</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.584Z</t>
+    <t>2026-06-18T06:05:09.060Z</t>
   </si>
   <si>
     <t>TC_CRUD_004: Read record list pagination</t>
   </si>
   <si>
-    <t>TC_0585</t>
+    <t>TC_9061</t>
   </si>
   <si>
     <t>TC_CRUD_005: Update record with valid data</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.585Z</t>
-  </si>
-  <si>
-    <t>TC_0586</t>
+    <t>2026-06-18T06:05:09.061Z</t>
   </si>
   <si>
     <t>TC_CRUD_006: Update record with invalid data</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.586Z</t>
-  </si>
-  <si>
-    <t>TC_0587</t>
+    <t>TC_9062</t>
   </si>
   <si>
     <t>TC_CRUD_007: Delete existing record</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.587Z</t>
-  </si>
-  <si>
-    <t>TC_0588</t>
+    <t>2026-06-18T06:05:09.062Z</t>
   </si>
   <si>
     <t>TC_CRUD_008: Cancel delete operation</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.588Z</t>
+    <t>TC_9063</t>
   </si>
   <si>
     <t>TC_CRUD_009: Confirmation dialogs on delete</t>
   </si>
   <si>
-    <t>TC_0589</t>
+    <t>2026-06-18T06:05:09.063Z</t>
   </si>
   <si>
     <t>TC_CRUD_010: Data persistence validation after refresh</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.589Z</t>
-  </si>
-  <si>
-    <t>TC_0590</t>
+    <t>TC_9064</t>
   </si>
   <si>
     <t>TC_CRUD_011: Create record with duplicate unique key</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.590Z</t>
+    <t>2026-06-18T06:05:09.064Z</t>
   </si>
   <si>
     <t>TC_CRUD_012: Read operation on non-existent record</t>
   </si>
   <si>
-    <t>TC_0591</t>
+    <t>TC_9065</t>
   </si>
   <si>
     <t>TC_CRUD_013: Bulk delete records</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.591Z</t>
+    <t>2026-06-18T06:05:09.065Z</t>
   </si>
   <si>
     <t>TC_CRUD_014: Bulk update records</t>
   </si>
   <si>
-    <t>TC_0592</t>
+    <t>TC_9066</t>
   </si>
   <si>
     <t>TC_CRUD_015: File upload during create</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.592Z</t>
+    <t>2026-06-18T06:05:09.066Z</t>
   </si>
   <si>
     <t>TC_CRUD_016: File download from read view</t>
   </si>
   <si>
-    <t>TC_0593</t>
+    <t>TC_9067</t>
   </si>
   <si>
     <t>TC_CRUD_017: Record state transition</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.593Z</t>
+    <t>2026-06-18T06:05:09.067Z</t>
   </si>
   <si>
     <t>TC_CRUD_018: Inline editing in list view</t>
   </si>
   <si>
-    <t>TC_0594</t>
+    <t>TC_9068</t>
   </si>
   <si>
     <t>TC_CRUD_019: Sort records by column</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.594Z</t>
+    <t>2026-06-18T06:05:09.068Z</t>
+  </si>
+  <si>
+    <t>TC_9069</t>
   </si>
   <si>
     <t>TC_CRUD_020: Filter records by criteria</t>
   </si>
   <si>
-    <t>TC_0595</t>
+    <t>2026-06-18T06:05:09.069Z</t>
+  </si>
+  <si>
+    <t>TC_9070</t>
   </si>
   <si>
     <t>TC_DASH_001: Dashboard loading</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.595Z</t>
-  </si>
-  <si>
-    <t>TC_0596</t>
+    <t>2026-06-18T06:05:09.070Z</t>
   </si>
   <si>
     <t>TC_DASH_002: Data rendering on widgets</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.596Z</t>
-  </si>
-  <si>
-    <t>TC_0597</t>
+    <t>TC_9071</t>
   </si>
   <si>
     <t>TC_DASH_003: Navigation cards clickability</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.597Z</t>
+    <t>2026-06-18T06:05:09.071Z</t>
+  </si>
+  <si>
+    <t>TC_9072</t>
   </si>
   <si>
     <t>TC_DASH_004: Widgets and metrics accuracy</t>
   </si>
   <si>
-    <t>TC_0598</t>
+    <t>2026-06-18T06:05:09.072Z</t>
   </si>
   <si>
     <t>TC_DASH_005: User profile access from dashboard</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.598Z</t>
-  </si>
-  <si>
     <t>TC_DASH_006: Dashboard refresh behavior</t>
   </si>
   <si>
-    <t>TC_0599</t>
+    <t>TC_9073</t>
   </si>
   <si>
     <t>TC_DASH_007: Sidebar toggle state persistence</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.599Z</t>
+    <t>2026-06-18T06:05:09.073Z</t>
   </si>
   <si>
     <t>TC_DASH_008: Notifications panel open/close</t>
   </si>
   <si>
-    <t>TC_0600</t>
+    <t>TC_9074</t>
   </si>
   <si>
     <t>TC_DASH_009: Recent activity feed updates</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.600Z</t>
+    <t>2026-06-18T06:05:09.074Z</t>
   </si>
   <si>
     <t>TC_DASH_010: Quick action buttons functionality</t>
   </si>
   <si>
-    <t>TC_0601</t>
-  </si>
-  <si>
     <t>TC_DASH_011: Data charts rendering</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.601Z</t>
+    <t>TC_9075</t>
   </si>
   <si>
     <t>TC_DASH_012: Data charts tooltips</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.602Z</t>
-  </si>
-  <si>
-    <t>TC_0603</t>
+    <t>2026-06-18T06:05:09.075Z</t>
   </si>
   <si>
     <t>TC_DASH_013: Dashboard layout responsiveness</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.603Z</t>
+    <t>TC_9076</t>
   </si>
   <si>
     <t>TC_DASH_014: Theme toggle effect on dashboard</t>
   </si>
   <si>
-    <t>TC_0604</t>
+    <t>2026-06-18T06:05:09.076Z</t>
   </si>
   <si>
     <t>TC_DASH_015: Loading spinners presence during data fetch</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:20.604Z</t>
-  </si>
-  <si>
-    <t>TC_2240</t>
+    <t>TC_2041</t>
   </si>
   <si>
     <t>should load the homepage</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.240Z</t>
-  </si>
-  <si>
-    <t>TC_2286</t>
+    <t>2026-06-18T06:05:52.041Z</t>
+  </si>
+  <si>
+    <t>TC_2320</t>
   </si>
   <si>
     <t>TC_NAV_001: Main menu navigation</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.286Z</t>
-  </si>
-  <si>
-    <t>TC_2288</t>
+    <t>2026-06-18T06:05:52.321Z</t>
+  </si>
+  <si>
+    <t>TC_2321</t>
   </si>
   <si>
     <t>TC_NAV_002: Breadcrumb verification</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.288Z</t>
+    <t>TC_2322</t>
   </si>
   <si>
     <t>TC_NAV_003: Browser back button navigation</t>
   </si>
   <si>
-    <t>TC_2289</t>
+    <t>2026-06-18T06:05:52.322Z</t>
   </si>
   <si>
     <t>TC_NAV_004: Browser forward button navigation</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.289Z</t>
+    <t>TC_2323</t>
   </si>
   <si>
     <t>TC_NAV_005: Page refresh behavior</t>
   </si>
   <si>
-    <t>TC_2290</t>
+    <t>2026-06-18T06:05:52.323Z</t>
   </si>
   <si>
     <t>TC_NAV_006: External links open in new tab</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.290Z</t>
+    <t>TC_2324</t>
   </si>
   <si>
     <t>TC_NAV_007: Internal anchor links navigation</t>
   </si>
   <si>
-    <t>TC_2291</t>
+    <t>2026-06-18T06:05:52.324Z</t>
   </si>
   <si>
     <t>TC_NAV_008: Sidebar collapse/expand navigation</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.291Z</t>
+    <t>TC_2325</t>
   </si>
   <si>
     <t>TC_NAV_009: Footer links navigation</t>
   </si>
   <si>
-    <t>TC_2292</t>
+    <t>2026-06-18T06:05:52.325Z</t>
   </si>
   <si>
     <t>TC_NAV_010: Tab navigation within pages</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.292Z</t>
-  </si>
-  <si>
-    <t>TC_2293</t>
+    <t>TC_2326</t>
   </si>
   <si>
     <t>TC_SEARCH_001: Basic search functionality</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.293Z</t>
+    <t>2026-06-18T06:05:52.326Z</t>
+  </si>
+  <si>
+    <t>TC_2327</t>
   </si>
   <si>
     <t>TC_SEARCH_002: Search with no results</t>
   </si>
   <si>
-    <t>TC_2294</t>
+    <t>2026-06-18T06:05:52.327Z</t>
   </si>
   <si>
     <t>TC_SEARCH_003: Search query persistence</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.294Z</t>
-  </si>
-  <si>
-    <t>TC_2295</t>
-  </si>
-  <si>
     <t>TC_SEARCH_004: Apply single filter</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.295Z</t>
-  </si>
-  <si>
-    <t>TC_2296</t>
+    <t>TC_2328</t>
   </si>
   <si>
     <t>TC_SEARCH_005: Apply multiple filters</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.296Z</t>
+    <t>2026-06-18T06:05:52.328Z</t>
+  </si>
+  <si>
+    <t>TC_2329</t>
   </si>
   <si>
     <t>TC_SEARCH_006: Clear all filters</t>
   </si>
   <si>
-    <t>TC_2297</t>
+    <t>2026-06-18T06:05:52.329Z</t>
   </si>
   <si>
     <t>TC_SEARCH_007: Sort by date ascending</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.297Z</t>
-  </si>
-  <si>
-    <t>TC_2298</t>
+    <t>TC_2330</t>
   </si>
   <si>
     <t>TC_SEARCH_008: Sort by date descending</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.298Z</t>
-  </si>
-  <si>
-    <t>TC_2299</t>
+    <t>2026-06-18T06:05:52.330Z</t>
   </si>
   <si>
     <t>TC_SEARCH_009: Sort by alphabet</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.299Z</t>
-  </si>
-  <si>
-    <t>TC_2301</t>
+    <t>TC_2332</t>
   </si>
   <si>
     <t>TC_SEARCH_010: Search highlighting in results</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.301Z</t>
-  </si>
-  <si>
-    <t>TC_7195</t>
+    <t>2026-06-18T06:05:52.332Z</t>
+  </si>
+  <si>
+    <t>TC_8210</t>
   </si>
   <si>
     <t>Deployable Status</t>
@@ -568,68 +529,64 @@
     <t>TC_E2E_001: Complete Student Journey (Register -&gt; Login -&gt; All Modules)</t>
   </si>
   <si>
-    <t xml:space="preserve">no such element: Unable to locate element: {"method":"css selector","selector":"input[placeholder="John Doe"]"}
-  (Session info: chrome=149.0.7827.104)</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>2026-06-18T05:58:27.195Z</t>
-  </si>
-  <si>
-    <t>C:\Users\dell\Desktop\pdd\WebApp\reports\screenshots\tc_e2e_001__complete_student_journey__register____login____all_modules__1781762307192.png</t>
-  </si>
-  <si>
-    <t>TC_1328</t>
+    <t>2026-06-18T06:05:38.210Z</t>
+  </si>
+  <si>
+    <t>TC_1422</t>
   </si>
   <si>
     <t>TC_E2E_002: Complete Admin Journey (Register -&gt; Login -&gt; Admin Dashboard)</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:41.328Z</t>
-  </si>
-  <si>
-    <t>TC_2862</t>
+    <t>2026-06-18T06:05:51.422Z</t>
+  </si>
+  <si>
+    <t>TC_2656</t>
   </si>
   <si>
     <t>TC_SMOKE_001: Validate application startup</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.862Z</t>
-  </si>
-  <si>
-    <t>TC_4135</t>
+    <t>2026-06-18T06:05:52.656Z</t>
+  </si>
+  <si>
+    <t>TC_3941</t>
   </si>
   <si>
     <t>TC_SMOKE_002: Validate login page accessibility</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:44.135Z</t>
-  </si>
-  <si>
-    <t>TC_4136</t>
+    <t>2026-06-18T06:05:53.941Z</t>
+  </si>
+  <si>
+    <t>TC_3942</t>
   </si>
   <si>
     <t>TC_SMOKE_003: Validate dashboard access (unauthorized)</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:44.136Z</t>
-  </si>
-  <si>
-    <t>TC_4137</t>
+    <t>2026-06-18T06:05:53.942Z</t>
+  </si>
+  <si>
+    <t>TC_3944</t>
   </si>
   <si>
     <t>TC_SMOKE_004: Validate primary business flow presence</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:44.137Z</t>
+    <t>2026-06-18T06:05:53.944Z</t>
+  </si>
+  <si>
+    <t>TC_3945</t>
   </si>
   <si>
     <t>TC_SMOKE_005: Validate 404 page for invalid route</t>
   </si>
   <si>
-    <t>TC_1329</t>
+    <t>2026-06-18T06:05:53.945Z</t>
+  </si>
+  <si>
+    <t>TC_1423</t>
   </si>
   <si>
     <t>Validation Test</t>
@@ -638,274 +595,238 @@
     <t>TC_ERR_001: Invalid URL routing (404)</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:41.329Z</t>
-  </si>
-  <si>
-    <t>TC_1330</t>
+    <t>2026-06-18T06:05:51.423Z</t>
+  </si>
+  <si>
+    <t>TC_1424</t>
   </si>
   <si>
     <t>TC_ERR_002: Server error rendering (500)</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:41.330Z</t>
+    <t>2026-06-18T06:05:51.424Z</t>
+  </si>
+  <si>
+    <t>TC_1425</t>
   </si>
   <si>
     <t>TC_ERR_003: Network disconnection handling</t>
   </si>
   <si>
-    <t>TC_1331</t>
+    <t>2026-06-18T06:05:51.425Z</t>
+  </si>
+  <si>
+    <t>TC_1426</t>
   </si>
   <si>
     <t>TC_ERR_004: Graceful degradation on API failure</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:41.331Z</t>
+    <t>2026-06-18T06:05:51.426Z</t>
   </si>
   <si>
     <t>TC_ERR_005: Form submission timeout handling</t>
   </si>
   <si>
-    <t>TC_1332</t>
+    <t>TC_1427</t>
   </si>
   <si>
     <t>TC_ERR_006: Invalid API response format handling</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:41.332Z</t>
-  </si>
-  <si>
-    <t>TC_1333</t>
+    <t>2026-06-18T06:05:51.427Z</t>
   </si>
   <si>
     <t>TC_ERR_007: Image loading failure fallback</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:41.333Z</t>
-  </si>
-  <si>
-    <t>TC_1336</t>
+    <t>TC_1429</t>
   </si>
   <si>
     <t>TC_ERR_008: Unauthorized API call handling (401/403)</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:41.336Z</t>
-  </si>
-  <si>
-    <t>TC_1337</t>
+    <t>2026-06-18T06:05:51.429Z</t>
   </si>
   <si>
     <t>TC_ERR_009: Rate limit exceeded handling (429)</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:41.337Z</t>
-  </si>
-  <si>
-    <t>TC_1338</t>
+    <t>TC_1430</t>
   </si>
   <si>
     <t>TC_ERR_010: Error boundary rendering in React/Vite</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:41.338Z</t>
-  </si>
-  <si>
-    <t>TC_1862</t>
+    <t>2026-06-18T06:05:51.430Z</t>
+  </si>
+  <si>
+    <t>TC_1742</t>
   </si>
   <si>
     <t>TC_FORM_001: Required field validation</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:41.862Z</t>
-  </si>
-  <si>
-    <t>TC_1863</t>
+    <t>2026-06-18T06:05:51.742Z</t>
+  </si>
+  <si>
+    <t>TC_1743</t>
   </si>
   <si>
     <t>TC_FORM_002: Invalid email format validation</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:41.863Z</t>
-  </si>
-  <si>
-    <t>TC_1864</t>
+    <t>2026-06-18T06:05:51.743Z</t>
   </si>
   <si>
     <t>TC_FORM_003: Boundary value testing for numbers</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:41.864Z</t>
+    <t>TC_1744</t>
   </si>
   <si>
     <t>TC_FORM_004: Empty field handling on submit</t>
   </si>
   <si>
-    <t>TC_1865</t>
+    <t>2026-06-18T06:05:51.744Z</t>
+  </si>
+  <si>
+    <t>TC_1745</t>
   </si>
   <si>
     <t>TC_FORM_005: Maximum length checks</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:41.865Z</t>
-  </si>
-  <si>
-    <t>TC_1866</t>
+    <t>2026-06-18T06:05:51.745Z</t>
   </si>
   <si>
     <t>TC_FORM_006: Minimum length checks</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:41.866Z</t>
-  </si>
-  <si>
-    <t>TC_1871</t>
+    <t>TC_1746</t>
   </si>
   <si>
     <t>TC_FORM_007: Numeric only validation</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:41.871Z</t>
-  </si>
-  <si>
-    <t>TC_1872</t>
+    <t>2026-06-18T06:05:51.746Z</t>
   </si>
   <si>
     <t>TC_FORM_008: Special character validation rejection</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:41.872Z</t>
-  </si>
-  <si>
-    <t>TC_1873</t>
+    <t>TC_1747</t>
   </si>
   <si>
     <t>TC_FORM_009: Special character validation acceptance</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:41.873Z</t>
-  </si>
-  <si>
-    <t>TC_1874</t>
+    <t>2026-06-18T06:05:51.747Z</t>
+  </si>
+  <si>
+    <t>TC_1749</t>
   </si>
   <si>
     <t>TC_FORM_010: Form reset functionality</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:41.874Z</t>
+    <t>2026-06-18T06:05:51.749Z</t>
+  </si>
+  <si>
+    <t>TC_1750</t>
   </si>
   <si>
     <t>TC_FORM_011: Date picker format validation</t>
   </si>
   <si>
-    <t>TC_1875</t>
+    <t>2026-06-18T06:05:51.750Z</t>
+  </si>
+  <si>
+    <t>TC_1751</t>
   </si>
   <si>
     <t>TC_FORM_012: Future date validation</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:41.875Z</t>
-  </si>
-  <si>
-    <t>TC_1876</t>
+    <t>2026-06-18T06:05:51.751Z</t>
   </si>
   <si>
     <t>TC_FORM_013: Past date validation</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:41.876Z</t>
+    <t>TC_1752</t>
   </si>
   <si>
     <t>TC_FORM_014: Dropdown selection validation</t>
   </si>
   <si>
-    <t>TC_1877</t>
+    <t>2026-06-18T06:05:51.752Z</t>
   </si>
   <si>
     <t>TC_FORM_015: Multi-select dropdown validation</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:41.877Z</t>
-  </si>
-  <si>
-    <t>TC_2303</t>
+    <t>TC_2333</t>
   </si>
   <si>
     <t>TC_SEC_001: Session persistence on reload</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.303Z</t>
-  </si>
-  <si>
-    <t>TC_2304</t>
+    <t>2026-06-18T06:05:52.333Z</t>
+  </si>
+  <si>
+    <t>TC_2334</t>
   </si>
   <si>
     <t>TC_SEC_002: Unauthorized access prevention to dashboard</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.304Z</t>
-  </si>
-  <si>
-    <t>TC_2305</t>
+    <t>2026-06-18T06:05:52.334Z</t>
   </si>
   <si>
     <t>TC_SEC_003: Protected route redirection to login</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.305Z</t>
+    <t>TC_2335</t>
   </si>
   <si>
     <t>TC_SEC_004: Logout invalidates session</t>
   </si>
   <si>
-    <t>TC_2306</t>
+    <t>2026-06-18T06:05:52.335Z</t>
   </si>
   <si>
     <t>TC_SEC_005: Role-based access control (Admin)</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.306Z</t>
-  </si>
-  <si>
-    <t>TC_2307</t>
+    <t>TC_2336</t>
   </si>
   <si>
     <t>TC_SEC_006: Role-based access control (User)</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.307Z</t>
+    <t>2026-06-18T06:05:52.336Z</t>
   </si>
   <si>
     <t>TC_SEC_007: XSS injection prevention in forms</t>
   </si>
   <si>
-    <t>TC_2308</t>
+    <t>TC_2337</t>
   </si>
   <si>
     <t>TC_SEC_008: SQL injection prevention in search</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.308Z</t>
-  </si>
-  <si>
-    <t>TC_2309</t>
+    <t>2026-06-18T06:05:52.337Z</t>
   </si>
   <si>
     <t>TC_SEC_009: CSRF token presence</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.309Z</t>
-  </si>
-  <si>
-    <t>TC_2310</t>
-  </si>
-  <si>
     <t>TC_SEC_010: Secure cookie attributes</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.310Z</t>
-  </si>
-  <si>
-    <t>TC_1861</t>
+    <t>TC_1741</t>
   </si>
   <si>
     <t>Form Validation Testing</t>
@@ -914,10 +835,10 @@
     <t>should show error for empty form submission</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:41.861Z</t>
-  </si>
-  <si>
-    <t>TC_2282</t>
+    <t>2026-06-18T06:05:51.741Z</t>
+  </si>
+  <si>
+    <t>TC_2319</t>
   </si>
   <si>
     <t>Login &amp; Signup Testing</t>
@@ -926,10 +847,10 @@
     <t>should navigate to login page</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:42.282Z</t>
-  </si>
-  <si>
-    <t>TC_4138</t>
+    <t>2026-06-18T06:05:52.319Z</t>
+  </si>
+  <si>
+    <t>TC_3948</t>
   </si>
   <si>
     <t>UI/UX Test</t>
@@ -938,67 +859,85 @@
     <t>TC_UI_001: Core element visibility on load</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:44.138Z</t>
-  </si>
-  <si>
-    <t>TC_4139</t>
+    <t>2026-06-18T06:05:53.948Z</t>
+  </si>
+  <si>
+    <t>TC_3950</t>
   </si>
   <si>
     <t>TC_UI_002: Button alignment and spacing</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:44.139Z</t>
+    <t>2026-06-18T06:05:53.950Z</t>
+  </si>
+  <si>
+    <t>TC_3951</t>
   </si>
   <si>
     <t>TC_UI_003: Form layout consistency</t>
   </si>
   <si>
-    <t>TC_4140</t>
+    <t>2026-06-18T06:05:53.951Z</t>
+  </si>
+  <si>
+    <t>TC_3953</t>
   </si>
   <si>
     <t>TC_UI_004: Responsive layout checks (Mobile viewport)</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:44.140Z</t>
+    <t>2026-06-18T06:05:53.953Z</t>
+  </si>
+  <si>
+    <t>TC_3954</t>
   </si>
   <si>
     <t>TC_UI_005: Responsive layout checks (Tablet viewport)</t>
   </si>
   <si>
-    <t>TC_4141</t>
+    <t>2026-06-18T06:05:53.954Z</t>
+  </si>
+  <si>
+    <t>TC_3955</t>
   </si>
   <si>
     <t>TC_UI_006: Navigation menu usability</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:44.141Z</t>
+    <t>2026-06-18T06:05:53.955Z</t>
   </si>
   <si>
     <t>TC_UI_007: Broken link detection across major pages</t>
   </si>
   <si>
-    <t>TC_4142</t>
+    <t>TC_3956</t>
   </si>
   <si>
     <t>TC_UI_008: Image loading and resolution verification</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:44.142Z</t>
+    <t>2026-06-18T06:05:53.956Z</t>
+  </si>
+  <si>
+    <t>TC_3957</t>
   </si>
   <si>
     <t>TC_UI_009: Font family and typography consistency</t>
   </si>
   <si>
-    <t>TC_4143</t>
+    <t>2026-06-18T06:05:53.957Z</t>
+  </si>
+  <si>
+    <t>TC_3958</t>
   </si>
   <si>
     <t>TC_UI_010: Color palette and contrast accessibility</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:44.143Z</t>
-  </si>
-  <si>
-    <t>TC_4144</t>
+    <t>2026-06-18T06:05:53.958Z</t>
+  </si>
+  <si>
+    <t>TC_3959</t>
   </si>
   <si>
     <t>Unit Testing</t>
@@ -1007,86 +946,125 @@
     <t>TC_UNIT_001: Validate password hashing utility logic</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:44.144Z</t>
+    <t>2026-06-18T06:05:53.959Z</t>
+  </si>
+  <si>
+    <t>TC_3960</t>
   </si>
   <si>
     <t>TC_UNIT_002: Validate email regex format utility</t>
   </si>
   <si>
+    <t>2026-06-18T06:05:53.960Z</t>
+  </si>
+  <si>
+    <t>TC_3962</t>
+  </si>
+  <si>
     <t>TC_UNIT_003: Validate URL parsing utility</t>
   </si>
   <si>
-    <t>TC_4145</t>
+    <t>2026-06-18T06:05:53.962Z</t>
+  </si>
+  <si>
+    <t>TC_3963</t>
   </si>
   <si>
     <t>TC_UNIT_004: Validate date formatting helper</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:44.145Z</t>
+    <t>2026-06-18T06:05:53.963Z</t>
+  </si>
+  <si>
+    <t>TC_3964</t>
   </si>
   <si>
     <t>TC_UNIT_005: Verify number currency formatting helper</t>
   </si>
   <si>
-    <t>TC_4146</t>
+    <t>2026-06-18T06:05:53.964Z</t>
+  </si>
+  <si>
+    <t>TC_3966</t>
   </si>
   <si>
     <t>TC_UNIT_006: Check application state reducer for login</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:44.146Z</t>
+    <t>2026-06-18T06:05:53.966Z</t>
   </si>
   <si>
     <t>TC_UNIT_007: Check application state reducer for logout</t>
   </si>
   <si>
-    <t>TC_4147</t>
+    <t>2026-06-18T06:05:53.967Z</t>
+  </si>
+  <si>
+    <t>TC_3968</t>
   </si>
   <si>
     <t>TC_UNIT_008: Validate local storage persistence helper</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:44.147Z</t>
+    <t>2026-06-18T06:05:53.968Z</t>
   </si>
   <si>
     <t>TC_UNIT_009: Test mock data generation for dashboard</t>
   </si>
   <si>
+    <t>TC_3969</t>
+  </si>
+  <si>
     <t>TC_UNIT_010: Validate theme toggler state boolean logic</t>
   </si>
   <si>
-    <t>TC_4148</t>
+    <t>2026-06-18T06:05:53.969Z</t>
+  </si>
+  <si>
+    <t>TC_3970</t>
   </si>
   <si>
     <t>TC_UNIT_011: Test array sorting utility for company list</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:44.148Z</t>
+    <t>2026-06-18T06:05:53.970Z</t>
+  </si>
+  <si>
+    <t>TC_3971</t>
   </si>
   <si>
     <t>TC_UNIT_012: Test pagination offset calculation utility</t>
   </si>
   <si>
+    <t>2026-06-18T06:05:53.971Z</t>
+  </si>
+  <si>
+    <t>TC_3972</t>
+  </si>
+  <si>
     <t>TC_UNIT_013: Verify input sanitization helper (XSS prevention)</t>
   </si>
   <si>
-    <t>TC_4149</t>
+    <t>2026-06-18T06:05:53.972Z</t>
   </si>
   <si>
     <t>TC_UNIT_014: Check token decoding function for expiration logic</t>
   </si>
   <si>
-    <t>2026-06-18T05:58:44.149Z</t>
+    <t>TC_3973</t>
   </si>
   <si>
     <t>TC_UNIT_015: Validate component classNames concatenation utility</t>
+  </si>
+  <si>
+    <t>2026-06-18T06:05:53.973Z</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1099,9 +1077,6 @@
     </font>
     <font>
       <color rgb="FF008000"/>
-    </font>
-    <font>
-      <color rgb="FFFF0000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1129,11 +1104,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1546,7 +1520,7 @@
         <v>17</v>
       </c>
       <c r="H2">
-        <v>193476</v>
+        <v>124075</v>
       </c>
       <c r="I2" t="s">
         <v>18</v>
@@ -1581,7 +1555,7 @@
         <v>17</v>
       </c>
       <c r="H3">
-        <v>122402</v>
+        <v>198094</v>
       </c>
       <c r="I3" t="s">
         <v>23</v>
@@ -1616,7 +1590,7 @@
         <v>17</v>
       </c>
       <c r="H4">
-        <v>80027</v>
+        <v>107976</v>
       </c>
       <c r="I4" t="s">
         <v>26</v>
@@ -1651,7 +1625,7 @@
         <v>17</v>
       </c>
       <c r="H5">
-        <v>108013</v>
+        <v>258982</v>
       </c>
       <c r="I5" t="s">
         <v>29</v>
@@ -1686,7 +1660,7 @@
         <v>17</v>
       </c>
       <c r="H6">
-        <v>230809</v>
+        <v>128694</v>
       </c>
       <c r="I6" t="s">
         <v>32</v>
@@ -1700,13 +1674,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -1721,10 +1695,10 @@
         <v>17</v>
       </c>
       <c r="H7">
-        <v>232304</v>
+        <v>204637</v>
       </c>
       <c r="I7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J7" t="s">
         <v>19</v>
@@ -1735,13 +1709,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -1756,10 +1730,10 @@
         <v>17</v>
       </c>
       <c r="H8">
-        <v>231006</v>
+        <v>144033</v>
       </c>
       <c r="I8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J8" t="s">
         <v>19</v>
@@ -1770,7 +1744,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -1791,10 +1765,10 @@
         <v>17</v>
       </c>
       <c r="H9">
-        <v>299671</v>
+        <v>65301</v>
       </c>
       <c r="I9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J9" t="s">
         <v>19</v>
@@ -1805,31 +1779,31 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
         <v>41</v>
       </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10">
+        <v>244498</v>
+      </c>
+      <c r="I10" t="s">
         <v>42</v>
-      </c>
-      <c r="D10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10">
-        <v>224630</v>
-      </c>
-      <c r="I10" t="s">
-        <v>43</v>
       </c>
       <c r="J10" t="s">
         <v>19</v>
@@ -1840,7 +1814,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -1861,7 +1835,7 @@
         <v>17</v>
       </c>
       <c r="H11">
-        <v>168554</v>
+        <v>205946</v>
       </c>
       <c r="I11" t="s">
         <v>45</v>
@@ -1896,10 +1870,10 @@
         <v>17</v>
       </c>
       <c r="H12">
-        <v>92138</v>
+        <v>176629</v>
       </c>
       <c r="I12" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J12" t="s">
         <v>19</v>
@@ -1910,7 +1884,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -1931,10 +1905,10 @@
         <v>17</v>
       </c>
       <c r="H13">
-        <v>274058</v>
+        <v>216772</v>
       </c>
       <c r="I13" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J13" t="s">
         <v>19</v>
@@ -1945,31 +1919,31 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s">
         <v>51</v>
       </c>
-      <c r="B14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14">
+        <v>206446</v>
+      </c>
+      <c r="I14" t="s">
         <v>52</v>
-      </c>
-      <c r="D14" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14">
-        <v>175802</v>
-      </c>
-      <c r="I14" t="s">
-        <v>53</v>
       </c>
       <c r="J14" t="s">
         <v>19</v>
@@ -1980,13 +1954,13 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
@@ -2001,10 +1975,10 @@
         <v>17</v>
       </c>
       <c r="H15">
-        <v>141675</v>
+        <v>74450</v>
       </c>
       <c r="I15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J15" t="s">
         <v>19</v>
@@ -2015,31 +1989,31 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
         <v>55</v>
       </c>
-      <c r="B16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16">
+        <v>132164</v>
+      </c>
+      <c r="I16" t="s">
         <v>56</v>
-      </c>
-      <c r="D16" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16">
-        <v>123063</v>
-      </c>
-      <c r="I16" t="s">
-        <v>57</v>
       </c>
       <c r="J16" t="s">
         <v>19</v>
@@ -2050,13 +2024,13 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
         <v>14</v>
@@ -2071,10 +2045,10 @@
         <v>17</v>
       </c>
       <c r="H17">
-        <v>143886</v>
+        <v>228879</v>
       </c>
       <c r="I17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J17" t="s">
         <v>19</v>
@@ -2085,31 +2059,31 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
         <v>59</v>
       </c>
-      <c r="B18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18">
+        <v>101673</v>
+      </c>
+      <c r="I18" t="s">
         <v>60</v>
-      </c>
-      <c r="D18" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18">
-        <v>62888</v>
-      </c>
-      <c r="I18" t="s">
-        <v>61</v>
       </c>
       <c r="J18" t="s">
         <v>19</v>
@@ -2120,13 +2094,13 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
@@ -2141,10 +2115,10 @@
         <v>17</v>
       </c>
       <c r="H19">
-        <v>189088</v>
+        <v>201736</v>
       </c>
       <c r="I19" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="J19" t="s">
         <v>19</v>
@@ -2155,13 +2129,13 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
         <v>14</v>
@@ -2176,10 +2150,10 @@
         <v>17</v>
       </c>
       <c r="H20">
-        <v>184931</v>
+        <v>96318</v>
       </c>
       <c r="I20" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J20" t="s">
         <v>19</v>
@@ -2190,13 +2164,13 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D21" t="s">
         <v>14</v>
@@ -2211,10 +2185,10 @@
         <v>17</v>
       </c>
       <c r="H21">
-        <v>65158</v>
+        <v>149869</v>
       </c>
       <c r="I21" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="J21" t="s">
         <v>19</v>
@@ -2225,31 +2199,31 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22">
+        <v>266254</v>
+      </c>
+      <c r="I22" t="s">
         <v>68</v>
-      </c>
-      <c r="B22" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22">
-        <v>226631</v>
-      </c>
-      <c r="I22" t="s">
-        <v>70</v>
       </c>
       <c r="J22" t="s">
         <v>19</v>
@@ -2260,13 +2234,13 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D23" t="s">
         <v>14</v>
@@ -2281,10 +2255,10 @@
         <v>17</v>
       </c>
       <c r="H23">
-        <v>234763</v>
+        <v>281538</v>
       </c>
       <c r="I23" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="J23" t="s">
         <v>19</v>
@@ -2295,13 +2269,13 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D24" t="s">
         <v>14</v>
@@ -2316,10 +2290,10 @@
         <v>17</v>
       </c>
       <c r="H24">
-        <v>194973</v>
+        <v>251969</v>
       </c>
       <c r="I24" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="J24" t="s">
         <v>19</v>
@@ -2330,13 +2304,13 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s">
         <v>14</v>
@@ -2351,10 +2325,10 @@
         <v>17</v>
       </c>
       <c r="H25">
-        <v>250754</v>
+        <v>296048</v>
       </c>
       <c r="I25" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="J25" t="s">
         <v>19</v>
@@ -2365,13 +2339,13 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B26" t="s">
         <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s">
         <v>14</v>
@@ -2386,10 +2360,10 @@
         <v>17</v>
       </c>
       <c r="H26">
-        <v>66509</v>
+        <v>137604</v>
       </c>
       <c r="I26" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="J26" t="s">
         <v>19</v>
@@ -2400,13 +2374,13 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B27" t="s">
         <v>12</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D27" t="s">
         <v>14</v>
@@ -2421,10 +2395,10 @@
         <v>17</v>
       </c>
       <c r="H27">
-        <v>275603</v>
+        <v>132565</v>
       </c>
       <c r="I27" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="J27" t="s">
         <v>19</v>
@@ -2435,13 +2409,13 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B28" t="s">
         <v>12</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D28" t="s">
         <v>14</v>
@@ -2456,10 +2430,10 @@
         <v>17</v>
       </c>
       <c r="H28">
-        <v>232568</v>
+        <v>70921</v>
       </c>
       <c r="I28" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="J28" t="s">
         <v>19</v>
@@ -2470,13 +2444,13 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B29" t="s">
         <v>12</v>
       </c>
       <c r="C29" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s">
         <v>14</v>
@@ -2491,10 +2465,10 @@
         <v>17</v>
       </c>
       <c r="H29">
-        <v>145565</v>
+        <v>170631</v>
       </c>
       <c r="I29" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="J29" t="s">
         <v>19</v>
@@ -2505,13 +2479,13 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s">
         <v>14</v>
@@ -2526,10 +2500,10 @@
         <v>17</v>
       </c>
       <c r="H30">
-        <v>101507</v>
+        <v>145591</v>
       </c>
       <c r="I30" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="J30" t="s">
         <v>19</v>
@@ -2540,13 +2514,13 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B31" t="s">
         <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D31" t="s">
         <v>14</v>
@@ -2561,10 +2535,10 @@
         <v>17</v>
       </c>
       <c r="H31">
-        <v>135710</v>
+        <v>174756</v>
       </c>
       <c r="I31" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="J31" t="s">
         <v>19</v>
@@ -2575,13 +2549,13 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B32" t="s">
         <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D32" t="s">
         <v>14</v>
@@ -2596,10 +2570,10 @@
         <v>17</v>
       </c>
       <c r="H32">
-        <v>80815</v>
+        <v>152736</v>
       </c>
       <c r="I32" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J32" t="s">
         <v>19</v>
@@ -2610,31 +2584,31 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>89</v>
+      </c>
+      <c r="B33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H33">
+        <v>264004</v>
+      </c>
+      <c r="I33" t="s">
         <v>91</v>
-      </c>
-      <c r="B33" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" t="s">
-        <v>94</v>
-      </c>
-      <c r="D33" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" t="s">
-        <v>15</v>
-      </c>
-      <c r="F33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H33">
-        <v>158377</v>
-      </c>
-      <c r="I33" t="s">
-        <v>93</v>
       </c>
       <c r="J33" t="s">
         <v>19</v>
@@ -2645,13 +2619,13 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D34" t="s">
         <v>14</v>
@@ -2666,10 +2640,10 @@
         <v>17</v>
       </c>
       <c r="H34">
-        <v>97571</v>
+        <v>223589</v>
       </c>
       <c r="I34" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J34" t="s">
         <v>19</v>
@@ -2680,13 +2654,13 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B35" t="s">
         <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D35" t="s">
         <v>14</v>
@@ -2701,10 +2675,10 @@
         <v>17</v>
       </c>
       <c r="H35">
-        <v>154779</v>
+        <v>285020</v>
       </c>
       <c r="I35" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="J35" t="s">
         <v>19</v>
@@ -2715,13 +2689,13 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B36" t="s">
         <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D36" t="s">
         <v>14</v>
@@ -2736,10 +2710,10 @@
         <v>17</v>
       </c>
       <c r="H36">
-        <v>107545</v>
+        <v>110014</v>
       </c>
       <c r="I36" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="J36" t="s">
         <v>19</v>
@@ -2750,31 +2724,31 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" t="s">
+        <v>15</v>
+      </c>
+      <c r="F37" t="s">
+        <v>16</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37">
+        <v>190440</v>
+      </c>
+      <c r="I37" t="s">
         <v>101</v>
-      </c>
-      <c r="B37" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" t="s">
-        <v>104</v>
-      </c>
-      <c r="D37" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" t="s">
-        <v>15</v>
-      </c>
-      <c r="F37" t="s">
-        <v>16</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H37">
-        <v>100861</v>
-      </c>
-      <c r="I37" t="s">
-        <v>103</v>
       </c>
       <c r="J37" t="s">
         <v>19</v>
@@ -2785,13 +2759,13 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B38" t="s">
         <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D38" t="s">
         <v>14</v>
@@ -2806,10 +2780,10 @@
         <v>17</v>
       </c>
       <c r="H38">
-        <v>243465</v>
+        <v>120599</v>
       </c>
       <c r="I38" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J38" t="s">
         <v>19</v>
@@ -2820,13 +2794,13 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B39" t="s">
         <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D39" t="s">
         <v>14</v>
@@ -2841,10 +2815,10 @@
         <v>17</v>
       </c>
       <c r="H39">
-        <v>260283</v>
+        <v>290455</v>
       </c>
       <c r="I39" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J39" t="s">
         <v>19</v>
@@ -2855,13 +2829,13 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B40" t="s">
         <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D40" t="s">
         <v>14</v>
@@ -2876,10 +2850,10 @@
         <v>17</v>
       </c>
       <c r="H40">
-        <v>263683</v>
+        <v>248564</v>
       </c>
       <c r="I40" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="J40" t="s">
         <v>19</v>
@@ -2890,13 +2864,13 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B41" t="s">
         <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D41" t="s">
         <v>14</v>
@@ -2911,10 +2885,10 @@
         <v>17</v>
       </c>
       <c r="H41">
-        <v>196862</v>
+        <v>234156</v>
       </c>
       <c r="I41" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="J41" t="s">
         <v>19</v>
@@ -2925,13 +2899,13 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B42" t="s">
         <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D42" t="s">
         <v>14</v>
@@ -2946,10 +2920,10 @@
         <v>17</v>
       </c>
       <c r="H42">
-        <v>127247</v>
+        <v>264241</v>
       </c>
       <c r="I42" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="J42" t="s">
         <v>19</v>
@@ -2960,13 +2934,13 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B43" t="s">
         <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D43" t="s">
         <v>14</v>
@@ -2981,10 +2955,10 @@
         <v>17</v>
       </c>
       <c r="H43">
-        <v>86237</v>
+        <v>183080</v>
       </c>
       <c r="I43" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="J43" t="s">
         <v>19</v>
@@ -2995,13 +2969,13 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B44" t="s">
         <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D44" t="s">
         <v>14</v>
@@ -3016,10 +2990,10 @@
         <v>17</v>
       </c>
       <c r="H44">
-        <v>140868</v>
+        <v>165714</v>
       </c>
       <c r="I44" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="J44" t="s">
         <v>19</v>
@@ -3030,13 +3004,13 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B45" t="s">
         <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D45" t="s">
         <v>14</v>
@@ -3051,10 +3025,10 @@
         <v>17</v>
       </c>
       <c r="H45">
-        <v>74381</v>
+        <v>260425</v>
       </c>
       <c r="I45" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="J45" t="s">
         <v>19</v>
@@ -3065,13 +3039,13 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B46" t="s">
         <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D46" t="s">
         <v>14</v>
@@ -3086,10 +3060,10 @@
         <v>17</v>
       </c>
       <c r="H46">
-        <v>288428</v>
+        <v>73424</v>
       </c>
       <c r="I46" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="J46" t="s">
         <v>19</v>
@@ -3100,13 +3074,13 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B47" t="s">
         <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D47" t="s">
         <v>14</v>
@@ -3121,10 +3095,10 @@
         <v>17</v>
       </c>
       <c r="H47">
-        <v>276544</v>
+        <v>123130</v>
       </c>
       <c r="I47" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="J47" t="s">
         <v>19</v>
@@ -3135,13 +3109,13 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="B48" t="s">
         <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D48" t="s">
         <v>14</v>
@@ -3156,10 +3130,10 @@
         <v>17</v>
       </c>
       <c r="H48">
-        <v>79463</v>
+        <v>94680</v>
       </c>
       <c r="I48" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="J48" t="s">
         <v>19</v>
@@ -3170,13 +3144,13 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D49" t="s">
         <v>14</v>
@@ -3191,10 +3165,10 @@
         <v>17</v>
       </c>
       <c r="H49">
-        <v>109714</v>
+        <v>138153</v>
       </c>
       <c r="I49" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="J49" t="s">
         <v>19</v>
@@ -3205,13 +3179,13 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B50" t="s">
         <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D50" t="s">
         <v>14</v>
@@ -3226,10 +3200,10 @@
         <v>17</v>
       </c>
       <c r="H50">
-        <v>61042</v>
+        <v>140666</v>
       </c>
       <c r="I50" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="J50" t="s">
         <v>19</v>
@@ -3240,13 +3214,13 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B51" t="s">
         <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D51" t="s">
         <v>14</v>
@@ -3261,10 +3235,10 @@
         <v>17</v>
       </c>
       <c r="H51">
-        <v>288944</v>
+        <v>260486</v>
       </c>
       <c r="I51" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="J51" t="s">
         <v>19</v>
@@ -3275,13 +3249,13 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B52" t="s">
         <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="D52" t="s">
         <v>14</v>
@@ -3296,10 +3270,10 @@
         <v>17</v>
       </c>
       <c r="H52">
-        <v>215549</v>
+        <v>174607</v>
       </c>
       <c r="I52" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J52" t="s">
         <v>19</v>
@@ -3310,13 +3284,13 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="B53" t="s">
         <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D53" t="s">
         <v>14</v>
@@ -3331,10 +3305,10 @@
         <v>17</v>
       </c>
       <c r="H53">
-        <v>86973</v>
+        <v>294408</v>
       </c>
       <c r="I53" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="J53" t="s">
         <v>19</v>
@@ -3345,13 +3319,13 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B54" t="s">
         <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D54" t="s">
         <v>14</v>
@@ -3366,10 +3340,10 @@
         <v>17</v>
       </c>
       <c r="H54">
-        <v>89890</v>
+        <v>202936</v>
       </c>
       <c r="I54" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="J54" t="s">
         <v>19</v>
@@ -3380,13 +3354,13 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="B55" t="s">
         <v>12</v>
       </c>
       <c r="C55" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D55" t="s">
         <v>14</v>
@@ -3401,10 +3375,10 @@
         <v>17</v>
       </c>
       <c r="H55">
-        <v>105484</v>
+        <v>206934</v>
       </c>
       <c r="I55" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="J55" t="s">
         <v>19</v>
@@ -3415,13 +3389,13 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B56" t="s">
         <v>12</v>
       </c>
       <c r="C56" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="D56" t="s">
         <v>14</v>
@@ -3436,10 +3410,10 @@
         <v>17</v>
       </c>
       <c r="H56">
-        <v>203933</v>
+        <v>125089</v>
       </c>
       <c r="I56" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="J56" t="s">
         <v>19</v>
@@ -3450,13 +3424,13 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="B57" t="s">
         <v>12</v>
       </c>
       <c r="C57" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D57" t="s">
         <v>14</v>
@@ -3471,10 +3445,10 @@
         <v>17</v>
       </c>
       <c r="H57">
-        <v>98835</v>
+        <v>188850</v>
       </c>
       <c r="I57" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="J57" t="s">
         <v>19</v>
@@ -3485,13 +3459,13 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B58" t="s">
         <v>12</v>
       </c>
       <c r="C58" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="D58" t="s">
         <v>14</v>
@@ -3506,10 +3480,10 @@
         <v>17</v>
       </c>
       <c r="H58">
-        <v>259417</v>
+        <v>251604</v>
       </c>
       <c r="I58" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="J58" t="s">
         <v>19</v>
@@ -3520,13 +3494,13 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="B59" t="s">
         <v>12</v>
       </c>
       <c r="C59" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D59" t="s">
         <v>14</v>
@@ -3541,10 +3515,10 @@
         <v>17</v>
       </c>
       <c r="H59">
-        <v>235388</v>
+        <v>278435</v>
       </c>
       <c r="I59" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="J59" t="s">
         <v>19</v>
@@ -3555,13 +3529,13 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="B60" t="s">
         <v>12</v>
       </c>
       <c r="C60" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="D60" t="s">
         <v>14</v>
@@ -3576,10 +3550,10 @@
         <v>17</v>
       </c>
       <c r="H60">
-        <v>111039</v>
+        <v>160016</v>
       </c>
       <c r="I60" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="J60" t="s">
         <v>19</v>
@@ -3590,13 +3564,13 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B61" t="s">
         <v>12</v>
       </c>
       <c r="C61" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D61" t="s">
         <v>14</v>
@@ -3611,10 +3585,10 @@
         <v>17</v>
       </c>
       <c r="H61">
-        <v>118188</v>
+        <v>166012</v>
       </c>
       <c r="I61" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="J61" t="s">
         <v>19</v>
@@ -3625,13 +3599,13 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="B62" t="s">
         <v>12</v>
       </c>
       <c r="C62" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D62" t="s">
         <v>14</v>
@@ -3646,10 +3620,10 @@
         <v>17</v>
       </c>
       <c r="H62">
-        <v>167249</v>
+        <v>137872</v>
       </c>
       <c r="I62" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="J62" t="s">
         <v>19</v>
@@ -3660,13 +3634,13 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="B63" t="s">
         <v>12</v>
       </c>
       <c r="C63" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="D63" t="s">
         <v>14</v>
@@ -3681,10 +3655,10 @@
         <v>17</v>
       </c>
       <c r="H63">
-        <v>241911</v>
+        <v>246983</v>
       </c>
       <c r="I63" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="J63" t="s">
         <v>19</v>
@@ -3695,13 +3669,13 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="B64" t="s">
         <v>12</v>
       </c>
       <c r="C64" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="D64" t="s">
         <v>14</v>
@@ -3716,10 +3690,10 @@
         <v>17</v>
       </c>
       <c r="H64">
-        <v>98735</v>
+        <v>288728</v>
       </c>
       <c r="I64" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="J64" t="s">
         <v>19</v>
@@ -3730,13 +3704,13 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B65" t="s">
         <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="D65" t="s">
         <v>14</v>
@@ -3751,10 +3725,10 @@
         <v>17</v>
       </c>
       <c r="H65">
-        <v>227058</v>
+        <v>213818</v>
       </c>
       <c r="I65" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J65" t="s">
         <v>19</v>
@@ -3765,13 +3739,13 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="B66" t="s">
         <v>12</v>
       </c>
       <c r="C66" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D66" t="s">
         <v>14</v>
@@ -3786,10 +3760,10 @@
         <v>17</v>
       </c>
       <c r="H66">
-        <v>97285</v>
+        <v>73150</v>
       </c>
       <c r="I66" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="J66" t="s">
         <v>19</v>
@@ -3800,13 +3774,13 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="B67" t="s">
         <v>12</v>
       </c>
       <c r="C67" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="D67" t="s">
         <v>14</v>
@@ -3821,10 +3795,10 @@
         <v>17</v>
       </c>
       <c r="H67">
-        <v>168663</v>
+        <v>282598</v>
       </c>
       <c r="I67" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="J67" t="s">
         <v>19</v>
@@ -3835,13 +3809,13 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="B68" t="s">
         <v>12</v>
       </c>
       <c r="C68" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="D68" t="s">
         <v>14</v>
@@ -3856,10 +3830,10 @@
         <v>17</v>
       </c>
       <c r="H68">
-        <v>86445</v>
+        <v>239909</v>
       </c>
       <c r="I68" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="J68" t="s">
         <v>19</v>
@@ -3870,13 +3844,13 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="B69" t="s">
         <v>12</v>
       </c>
       <c r="C69" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="D69" t="s">
         <v>14</v>
@@ -3891,10 +3865,10 @@
         <v>17</v>
       </c>
       <c r="H69">
-        <v>63415</v>
+        <v>98017</v>
       </c>
       <c r="I69" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="J69" t="s">
         <v>19</v>
@@ -3963,13 +3937,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="B2" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="C2" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -3978,19 +3952,19 @@
         <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>184</v>
+        <v>16</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="H2">
-        <v>280673</v>
+        <v>231308</v>
       </c>
       <c r="I2" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="J2" t="s">
-        <v>186</v>
+        <v>19</v>
       </c>
       <c r="K2" t="s">
         <v>20</v>
@@ -3998,13 +3972,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="B3" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="C3" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -4019,10 +3993,10 @@
         <v>17</v>
       </c>
       <c r="H3">
-        <v>247375</v>
+        <v>126094</v>
       </c>
       <c r="I3" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
@@ -4033,13 +4007,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="B4" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="C4" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -4054,10 +4028,10 @@
         <v>17</v>
       </c>
       <c r="H4">
-        <v>142519</v>
+        <v>129188</v>
       </c>
       <c r="I4" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -4068,13 +4042,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="B5" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="C5" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -4089,10 +4063,10 @@
         <v>17</v>
       </c>
       <c r="H5">
-        <v>222714</v>
+        <v>252944</v>
       </c>
       <c r="I5" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="J5" t="s">
         <v>19</v>
@@ -4103,14 +4077,14 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="B6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" t="s">
         <v>181</v>
       </c>
-      <c r="C6" t="s">
-        <v>197</v>
-      </c>
       <c r="D6" t="s">
         <v>14</v>
       </c>
@@ -4124,10 +4098,10 @@
         <v>17</v>
       </c>
       <c r="H6">
-        <v>65594</v>
+        <v>275003</v>
       </c>
       <c r="I6" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
@@ -4138,13 +4112,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="B7" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="C7" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -4159,10 +4133,10 @@
         <v>17</v>
       </c>
       <c r="H7">
-        <v>221852</v>
+        <v>98345</v>
       </c>
       <c r="I7" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="J7" t="s">
         <v>19</v>
@@ -4173,13 +4147,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="B8" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="C8" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -4194,10 +4168,10 @@
         <v>17</v>
       </c>
       <c r="H8">
-        <v>236283</v>
+        <v>208081</v>
       </c>
       <c r="I8" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="J8" t="s">
         <v>19</v>
@@ -4266,13 +4240,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="B2" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C2" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -4287,10 +4261,10 @@
         <v>17</v>
       </c>
       <c r="H2">
-        <v>219281</v>
+        <v>224154</v>
       </c>
       <c r="I2" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
@@ -4301,13 +4275,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="B3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C3" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -4322,10 +4296,10 @@
         <v>17</v>
       </c>
       <c r="H3">
-        <v>93057</v>
+        <v>203022</v>
       </c>
       <c r="I3" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
@@ -4336,13 +4310,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="B4" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C4" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -4357,10 +4331,10 @@
         <v>17</v>
       </c>
       <c r="H4">
-        <v>62980</v>
+        <v>250813</v>
       </c>
       <c r="I4" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -4371,13 +4345,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="B5" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C5" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -4392,10 +4366,10 @@
         <v>17</v>
       </c>
       <c r="H5">
-        <v>148806</v>
+        <v>125925</v>
       </c>
       <c r="I5" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="J5" t="s">
         <v>19</v>
@@ -4406,13 +4380,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="B6" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C6" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -4427,10 +4401,10 @@
         <v>17</v>
       </c>
       <c r="H6">
-        <v>236191</v>
+        <v>103276</v>
       </c>
       <c r="I6" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
@@ -4441,14 +4415,14 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="B7" t="s">
+        <v>190</v>
+      </c>
+      <c r="C7" t="s">
         <v>204</v>
       </c>
-      <c r="C7" t="s">
-        <v>216</v>
-      </c>
       <c r="D7" t="s">
         <v>14</v>
       </c>
@@ -4462,10 +4436,10 @@
         <v>17</v>
       </c>
       <c r="H7">
-        <v>140405</v>
+        <v>138907</v>
       </c>
       <c r="I7" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="J7" t="s">
         <v>19</v>
@@ -4476,13 +4450,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="B8" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C8" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -4497,10 +4471,10 @@
         <v>17</v>
       </c>
       <c r="H8">
-        <v>222092</v>
+        <v>237037</v>
       </c>
       <c r="I8" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="J8" t="s">
         <v>19</v>
@@ -4511,13 +4485,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="B9" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C9" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -4532,10 +4506,10 @@
         <v>17</v>
       </c>
       <c r="H9">
-        <v>110395</v>
+        <v>123430</v>
       </c>
       <c r="I9" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="J9" t="s">
         <v>19</v>
@@ -4546,13 +4520,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="B10" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C10" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -4567,10 +4541,10 @@
         <v>17</v>
       </c>
       <c r="H10">
-        <v>232702</v>
+        <v>93835</v>
       </c>
       <c r="I10" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="J10" t="s">
         <v>19</v>
@@ -4581,13 +4555,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="B11" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C11" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -4602,10 +4576,10 @@
         <v>17</v>
       </c>
       <c r="H11">
-        <v>168864</v>
+        <v>219373</v>
       </c>
       <c r="I11" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="J11" t="s">
         <v>19</v>
@@ -4616,13 +4590,13 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="B12" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C12" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
@@ -4637,10 +4611,10 @@
         <v>17</v>
       </c>
       <c r="H12">
-        <v>122200</v>
+        <v>159451</v>
       </c>
       <c r="I12" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="J12" t="s">
         <v>19</v>
@@ -4651,13 +4625,13 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="B13" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C13" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -4672,10 +4646,10 @@
         <v>17</v>
       </c>
       <c r="H13">
-        <v>108687</v>
+        <v>269017</v>
       </c>
       <c r="I13" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="J13" t="s">
         <v>19</v>
@@ -4686,13 +4660,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="B14" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C14" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="D14" t="s">
         <v>14</v>
@@ -4707,10 +4681,10 @@
         <v>17</v>
       </c>
       <c r="H14">
-        <v>286058</v>
+        <v>127490</v>
       </c>
       <c r="I14" t="s">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="J14" t="s">
         <v>19</v>
@@ -4721,13 +4695,13 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="B15" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C15" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
@@ -4742,10 +4716,10 @@
         <v>17</v>
       </c>
       <c r="H15">
-        <v>252718</v>
+        <v>256749</v>
       </c>
       <c r="I15" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="J15" t="s">
         <v>19</v>
@@ -4756,13 +4730,13 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="B16" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C16" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="D16" t="s">
         <v>14</v>
@@ -4777,10 +4751,10 @@
         <v>17</v>
       </c>
       <c r="H16">
-        <v>68425</v>
+        <v>292489</v>
       </c>
       <c r="I16" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="J16" t="s">
         <v>19</v>
@@ -4791,13 +4765,13 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="B17" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C17" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="D17" t="s">
         <v>14</v>
@@ -4812,10 +4786,10 @@
         <v>17</v>
       </c>
       <c r="H17">
-        <v>289794</v>
+        <v>121936</v>
       </c>
       <c r="I17" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="J17" t="s">
         <v>19</v>
@@ -4826,13 +4800,13 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="B18" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C18" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="D18" t="s">
         <v>14</v>
@@ -4847,10 +4821,10 @@
         <v>17</v>
       </c>
       <c r="H18">
-        <v>245096</v>
+        <v>111415</v>
       </c>
       <c r="I18" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="J18" t="s">
         <v>19</v>
@@ -4861,13 +4835,13 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>249</v>
+        <v>228</v>
       </c>
       <c r="B19" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C19" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
@@ -4882,10 +4856,10 @@
         <v>17</v>
       </c>
       <c r="H19">
-        <v>147894</v>
+        <v>296766</v>
       </c>
       <c r="I19" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="J19" t="s">
         <v>19</v>
@@ -4896,13 +4870,13 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="B20" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C20" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="D20" t="s">
         <v>14</v>
@@ -4917,10 +4891,10 @@
         <v>17</v>
       </c>
       <c r="H20">
-        <v>65125</v>
+        <v>205372</v>
       </c>
       <c r="I20" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="J20" t="s">
         <v>19</v>
@@ -4931,13 +4905,13 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C21" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="D21" t="s">
         <v>14</v>
@@ -4952,10 +4926,10 @@
         <v>17</v>
       </c>
       <c r="H21">
-        <v>260739</v>
+        <v>298877</v>
       </c>
       <c r="I21" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="J21" t="s">
         <v>19</v>
@@ -4966,13 +4940,13 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="B22" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C22" t="s">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="D22" t="s">
         <v>14</v>
@@ -4987,10 +4961,10 @@
         <v>17</v>
       </c>
       <c r="H22">
-        <v>157411</v>
+        <v>200262</v>
       </c>
       <c r="I22" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="J22" t="s">
         <v>19</v>
@@ -5001,13 +4975,13 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C23" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="D23" t="s">
         <v>14</v>
@@ -5022,10 +4996,10 @@
         <v>17</v>
       </c>
       <c r="H23">
-        <v>91526</v>
+        <v>278277</v>
       </c>
       <c r="I23" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="J23" t="s">
         <v>19</v>
@@ -5036,13 +5010,13 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C24" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="D24" t="s">
         <v>14</v>
@@ -5057,10 +5031,10 @@
         <v>17</v>
       </c>
       <c r="H24">
-        <v>79600</v>
+        <v>79846</v>
       </c>
       <c r="I24" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="J24" t="s">
         <v>19</v>
@@ -5071,13 +5045,13 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C25" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="D25" t="s">
         <v>14</v>
@@ -5092,10 +5066,10 @@
         <v>17</v>
       </c>
       <c r="H25">
-        <v>122861</v>
+        <v>269987</v>
       </c>
       <c r="I25" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="J25" t="s">
         <v>19</v>
@@ -5106,13 +5080,13 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="B26" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C26" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="D26" t="s">
         <v>14</v>
@@ -5127,10 +5101,10 @@
         <v>17</v>
       </c>
       <c r="H26">
-        <v>115885</v>
+        <v>235616</v>
       </c>
       <c r="I26" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="J26" t="s">
         <v>19</v>
@@ -5141,13 +5115,13 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="B27" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C27" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="D27" t="s">
         <v>14</v>
@@ -5162,10 +5136,10 @@
         <v>17</v>
       </c>
       <c r="H27">
-        <v>69326</v>
+        <v>140452</v>
       </c>
       <c r="I27" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="J27" t="s">
         <v>19</v>
@@ -5176,13 +5150,13 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="B28" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C28" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="D28" t="s">
         <v>14</v>
@@ -5197,10 +5171,10 @@
         <v>17</v>
       </c>
       <c r="H28">
-        <v>163925</v>
+        <v>110126</v>
       </c>
       <c r="I28" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="J28" t="s">
         <v>19</v>
@@ -5211,13 +5185,13 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="B29" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C29" t="s">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="D29" t="s">
         <v>14</v>
@@ -5232,10 +5206,10 @@
         <v>17</v>
       </c>
       <c r="H29">
-        <v>240447</v>
+        <v>124024</v>
       </c>
       <c r="I29" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="J29" t="s">
         <v>19</v>
@@ -5246,13 +5220,13 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="B30" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C30" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="D30" t="s">
         <v>14</v>
@@ -5267,10 +5241,10 @@
         <v>17</v>
       </c>
       <c r="H30">
-        <v>126672</v>
+        <v>168225</v>
       </c>
       <c r="I30" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="J30" t="s">
         <v>19</v>
@@ -5281,13 +5255,13 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="B31" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C31" t="s">
-        <v>280</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
         <v>14</v>
@@ -5302,10 +5276,10 @@
         <v>17</v>
       </c>
       <c r="H31">
-        <v>99400</v>
+        <v>104368</v>
       </c>
       <c r="I31" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="J31" t="s">
         <v>19</v>
@@ -5316,13 +5290,13 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="B32" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C32" t="s">
-        <v>283</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
         <v>14</v>
@@ -5337,10 +5311,10 @@
         <v>17</v>
       </c>
       <c r="H32">
-        <v>208774</v>
+        <v>239128</v>
       </c>
       <c r="I32" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="J32" t="s">
         <v>19</v>
@@ -5351,13 +5325,13 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="B33" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C33" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="D33" t="s">
         <v>14</v>
@@ -5372,10 +5346,10 @@
         <v>17</v>
       </c>
       <c r="H33">
-        <v>288594</v>
+        <v>231464</v>
       </c>
       <c r="I33" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="J33" t="s">
         <v>19</v>
@@ -5386,13 +5360,13 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="B34" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C34" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="D34" t="s">
         <v>14</v>
@@ -5407,10 +5381,10 @@
         <v>17</v>
       </c>
       <c r="H34">
-        <v>68237</v>
+        <v>254978</v>
       </c>
       <c r="I34" t="s">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="J34" t="s">
         <v>19</v>
@@ -5421,13 +5395,13 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="B35" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C35" t="s">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="D35" t="s">
         <v>14</v>
@@ -5442,10 +5416,10 @@
         <v>17</v>
       </c>
       <c r="H35">
-        <v>141525</v>
+        <v>157984</v>
       </c>
       <c r="I35" t="s">
-        <v>291</v>
+        <v>266</v>
       </c>
       <c r="J35" t="s">
         <v>19</v>
@@ -5456,13 +5430,13 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>292</v>
+        <v>264</v>
       </c>
       <c r="B36" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C36" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="D36" t="s">
         <v>14</v>
@@ -5477,10 +5451,10 @@
         <v>17</v>
       </c>
       <c r="H36">
-        <v>76962</v>
+        <v>177855</v>
       </c>
       <c r="I36" t="s">
-        <v>294</v>
+        <v>266</v>
       </c>
       <c r="J36" t="s">
         <v>19</v>
@@ -5549,13 +5523,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="B2" t="s">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="C2" t="s">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -5570,10 +5544,10 @@
         <v>17</v>
       </c>
       <c r="H2">
-        <v>224452</v>
+        <v>118307</v>
       </c>
       <c r="I2" t="s">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
@@ -5642,13 +5616,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="B2" t="s">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="C2" t="s">
-        <v>301</v>
+        <v>275</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -5663,10 +5637,10 @@
         <v>17</v>
       </c>
       <c r="H2">
-        <v>71503</v>
+        <v>158540</v>
       </c>
       <c r="I2" t="s">
-        <v>302</v>
+        <v>276</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
@@ -5735,13 +5709,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="B2" t="s">
-        <v>304</v>
+        <v>278</v>
       </c>
       <c r="C2" t="s">
-        <v>305</v>
+        <v>279</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -5756,10 +5730,10 @@
         <v>17</v>
       </c>
       <c r="H2">
-        <v>145359</v>
+        <v>280835</v>
       </c>
       <c r="I2" t="s">
-        <v>306</v>
+        <v>280</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
@@ -5770,13 +5744,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>307</v>
+        <v>281</v>
       </c>
       <c r="B3" t="s">
-        <v>304</v>
+        <v>278</v>
       </c>
       <c r="C3" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -5791,10 +5765,10 @@
         <v>17</v>
       </c>
       <c r="H3">
-        <v>296756</v>
+        <v>136992</v>
       </c>
       <c r="I3" t="s">
-        <v>309</v>
+        <v>283</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
@@ -5805,13 +5779,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="B4" t="s">
-        <v>304</v>
+        <v>278</v>
       </c>
       <c r="C4" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -5826,10 +5800,10 @@
         <v>17</v>
       </c>
       <c r="H4">
-        <v>97187</v>
+        <v>114230</v>
       </c>
       <c r="I4" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -5840,13 +5814,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>311</v>
+        <v>287</v>
       </c>
       <c r="B5" t="s">
-        <v>304</v>
+        <v>278</v>
       </c>
       <c r="C5" t="s">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -5861,10 +5835,10 @@
         <v>17</v>
       </c>
       <c r="H5">
-        <v>185922</v>
+        <v>204390</v>
       </c>
       <c r="I5" t="s">
-        <v>313</v>
+        <v>289</v>
       </c>
       <c r="J5" t="s">
         <v>19</v>
@@ -5875,13 +5849,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>311</v>
+        <v>290</v>
       </c>
       <c r="B6" t="s">
-        <v>304</v>
+        <v>278</v>
       </c>
       <c r="C6" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -5896,10 +5870,10 @@
         <v>17</v>
       </c>
       <c r="H6">
-        <v>67022</v>
+        <v>152641</v>
       </c>
       <c r="I6" t="s">
-        <v>313</v>
+        <v>292</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
@@ -5910,13 +5884,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>315</v>
+        <v>293</v>
       </c>
       <c r="B7" t="s">
-        <v>304</v>
+        <v>278</v>
       </c>
       <c r="C7" t="s">
-        <v>316</v>
+        <v>294</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -5931,10 +5905,10 @@
         <v>17</v>
       </c>
       <c r="H7">
-        <v>138490</v>
+        <v>100692</v>
       </c>
       <c r="I7" t="s">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="J7" t="s">
         <v>19</v>
@@ -5945,13 +5919,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>315</v>
+        <v>293</v>
       </c>
       <c r="B8" t="s">
-        <v>304</v>
+        <v>278</v>
       </c>
       <c r="C8" t="s">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -5966,10 +5940,10 @@
         <v>17</v>
       </c>
       <c r="H8">
-        <v>114300</v>
+        <v>297392</v>
       </c>
       <c r="I8" t="s">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="J8" t="s">
         <v>19</v>
@@ -5980,13 +5954,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>319</v>
+        <v>297</v>
       </c>
       <c r="B9" t="s">
-        <v>304</v>
+        <v>278</v>
       </c>
       <c r="C9" t="s">
-        <v>320</v>
+        <v>298</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -6001,10 +5975,10 @@
         <v>17</v>
       </c>
       <c r="H9">
-        <v>119072</v>
+        <v>295451</v>
       </c>
       <c r="I9" t="s">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="J9" t="s">
         <v>19</v>
@@ -6015,13 +5989,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="B10" t="s">
-        <v>304</v>
+        <v>278</v>
       </c>
       <c r="C10" t="s">
-        <v>322</v>
+        <v>301</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -6036,10 +6010,10 @@
         <v>17</v>
       </c>
       <c r="H10">
-        <v>150498</v>
+        <v>104826</v>
       </c>
       <c r="I10" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
       <c r="J10" t="s">
         <v>19</v>
@@ -6050,14 +6024,14 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="B11" t="s">
+        <v>278</v>
+      </c>
+      <c r="C11" t="s">
         <v>304</v>
       </c>
-      <c r="C11" t="s">
-        <v>324</v>
-      </c>
       <c r="D11" t="s">
         <v>14</v>
       </c>
@@ -6071,10 +6045,10 @@
         <v>17</v>
       </c>
       <c r="H11">
-        <v>221659</v>
+        <v>278716</v>
       </c>
       <c r="I11" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="J11" t="s">
         <v>19</v>
@@ -6143,13 +6117,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="B2" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="C2" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -6164,10 +6138,10 @@
         <v>17</v>
       </c>
       <c r="H2">
-        <v>247014</v>
+        <v>195185</v>
       </c>
       <c r="I2" t="s">
-        <v>329</v>
+        <v>309</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
@@ -6178,13 +6152,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="B3" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="C3" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -6199,10 +6173,10 @@
         <v>17</v>
       </c>
       <c r="H3">
-        <v>236121</v>
+        <v>251639</v>
       </c>
       <c r="I3" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
@@ -6213,13 +6187,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="B4" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="C4" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -6234,10 +6208,10 @@
         <v>17</v>
       </c>
       <c r="H4">
-        <v>257039</v>
+        <v>216749</v>
       </c>
       <c r="I4" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -6248,13 +6222,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="B5" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="C5" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -6269,10 +6243,10 @@
         <v>17</v>
       </c>
       <c r="H5">
-        <v>172709</v>
+        <v>130607</v>
       </c>
       <c r="I5" t="s">
-        <v>334</v>
+        <v>318</v>
       </c>
       <c r="J5" t="s">
         <v>19</v>
@@ -6283,13 +6257,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="B6" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="C6" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -6304,10 +6278,10 @@
         <v>17</v>
       </c>
       <c r="H6">
-        <v>137780</v>
+        <v>69733</v>
       </c>
       <c r="I6" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
@@ -6318,13 +6292,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="B7" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="C7" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -6339,10 +6313,10 @@
         <v>17</v>
       </c>
       <c r="H7">
-        <v>115642</v>
+        <v>86814</v>
       </c>
       <c r="I7" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="J7" t="s">
         <v>19</v>
@@ -6353,13 +6327,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="B8" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="C8" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -6374,10 +6348,10 @@
         <v>17</v>
       </c>
       <c r="H8">
-        <v>255031</v>
+        <v>196526</v>
       </c>
       <c r="I8" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="J8" t="s">
         <v>19</v>
@@ -6388,13 +6362,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="B9" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="C9" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -6409,10 +6383,10 @@
         <v>17</v>
       </c>
       <c r="H9">
-        <v>160184</v>
+        <v>197330</v>
       </c>
       <c r="I9" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="J9" t="s">
         <v>19</v>
@@ -6423,13 +6397,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="B10" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="C10" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -6444,10 +6418,10 @@
         <v>17</v>
       </c>
       <c r="H10">
-        <v>92180</v>
+        <v>179446</v>
       </c>
       <c r="I10" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="J10" t="s">
         <v>19</v>
@@ -6458,13 +6432,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="B11" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="C11" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -6479,10 +6453,10 @@
         <v>17</v>
       </c>
       <c r="H11">
-        <v>226882</v>
+        <v>178023</v>
       </c>
       <c r="I11" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="J11" t="s">
         <v>19</v>
@@ -6493,13 +6467,13 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="B12" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="C12" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
@@ -6514,10 +6488,10 @@
         <v>17</v>
       </c>
       <c r="H12">
-        <v>190210</v>
+        <v>148749</v>
       </c>
       <c r="I12" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="J12" t="s">
         <v>19</v>
@@ -6528,13 +6502,13 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="B13" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="C13" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -6549,10 +6523,10 @@
         <v>17</v>
       </c>
       <c r="H13">
-        <v>286302</v>
+        <v>227970</v>
       </c>
       <c r="I13" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="J13" t="s">
         <v>19</v>
@@ -6563,13 +6537,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B14" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="C14" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="D14" t="s">
         <v>14</v>
@@ -6584,10 +6558,10 @@
         <v>17</v>
       </c>
       <c r="H14">
-        <v>203699</v>
+        <v>171614</v>
       </c>
       <c r="I14" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="J14" t="s">
         <v>19</v>
@@ -6598,13 +6572,13 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="B15" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="C15" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
@@ -6619,10 +6593,10 @@
         <v>17</v>
       </c>
       <c r="H15">
-        <v>198732</v>
+        <v>141306</v>
       </c>
       <c r="I15" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="J15" t="s">
         <v>19</v>
@@ -6633,13 +6607,13 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B16" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="C16" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="D16" t="s">
         <v>14</v>
@@ -6654,10 +6628,10 @@
         <v>17</v>
       </c>
       <c r="H16">
-        <v>248812</v>
+        <v>192282</v>
       </c>
       <c r="I16" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="J16" t="s">
         <v>19</v>
